--- a/data/ARC Storm Surge Shelter Demand.xlsx
+++ b/data/ARC Storm Surge Shelter Demand.xlsx
@@ -1,17 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/54fa78dadb255002/Documents/Heinz/Spring 2026/94-739 Capstone/ARC_Capstone/notebooks/repo/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9AB5DFE02E429FF0E24E20D6E25A8F1C4D155B9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="16800" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Interface" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Data Dictionary" sheetId="2" r:id="rId5"/>
+    <sheet name="Interface" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Dictionary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="County">#REF!</definedName>
     <definedName name="Feeding">#REF!</definedName>
-    <definedName name="County">#REF!</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="iES2mZTaGmdro8aTTATSsoj6stkWf6orN7HaZNde+SM="/>
     </ext>
@@ -20,30 +41,48 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="C33">
+    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAB3yg9fcg
+Megan Forry    (2026-04-21 04:13:26)
+capitalized</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB3yg9fck
 Megan Forry    (2026-04-21 04:13:34)
 capitalized</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="C27">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAB3yg9fcg
-Megan Forry    (2026-04-21 04:13:26)
-capitalized</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhjoU/YCBZDxrOJbS+LXCmpUATuDA=="/>
     </ext>
   </extLst>
@@ -274,19 +313,21 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Destroyed, Major, Minor
 </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>(Default: Destroyed)</t>
     </r>
@@ -297,19 +338,21 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Destroyed, Major, Minor
 </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>(Default: Destroyed)</t>
     </r>
@@ -320,19 +363,21 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Destroyed, Major, Minor
 </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>(Default: Major)</t>
     </r>
@@ -343,19 +388,21 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Destroyed, Major, Minor
 </t>
     </r>
     <r>
       <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>(Default: Minor)</t>
     </r>
@@ -395,149 +442,177 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="28.0"/>
+      <sz val="28"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
-    <font/>
     <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FF224622"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="12"/>
       <color rgb="FF224622"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+      <color rgb="FF224622"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="17"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF467886"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF467886"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF467886"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="60.0"/>
+      <sz val="60"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -546,7 +621,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -592,73 +667,107 @@
     </fill>
   </fills>
   <borders count="28">
-    <border/>
-    <border>
-      <left/>
-      <top/>
-    </border>
-    <border>
-      <top/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <bottom/>
-    </border>
-    <border>
-      <bottom/>
-    </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
+      <right/>
       <top/>
       <bottom/>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color theme="1"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -670,10 +779,15 @@
       <top style="thin">
         <color rgb="FFFFFFFF"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -688,13 +802,16 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -709,6 +826,7 @@
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -720,14 +838,19 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -739,6 +862,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -750,19 +875,28 @@
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -771,11 +905,18 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -784,341 +925,309 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="9" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="82">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="13" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="14" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="6" fontId="15" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="22" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="8" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="8" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="24" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAE2D5"/>
+          <bgColor rgb="FFFAE2D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="5"/>
           <bgColor theme="5"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAE2D5"/>
-          <bgColor rgb="FFFAE2D5"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Data Dictionary-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Data Dictionary-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -1129,11 +1238,17 @@
     <xdr:ext cx="2314575" cy="1543050"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="2" name="image1.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1150,25 +1265,21 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E29" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:E29">
   <tableColumns count="5">
-    <tableColumn name="Step" id="1"/>
-    <tableColumn name="Variable Name" id="2"/>
-    <tableColumn name="Definition" id="3"/>
-    <tableColumn name="Data Type" id="4"/>
-    <tableColumn name="Allowed Values" id="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Step"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Variable Name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Definition"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Data Type"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Allowed Values"/>
   </tableColumns>
-  <tableStyleInfo name="Data Dictionary-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Data Dictionary-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1358,388 +1469,411 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.0"/>
-    <col customWidth="1" min="2" max="2" width="26.67"/>
-    <col customWidth="1" min="3" max="3" width="27.0"/>
-    <col customWidth="1" min="4" max="4" width="27.33"/>
-    <col customWidth="1" min="5" max="5" width="31.67"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="70.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" ht="129.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+    </row>
+    <row r="2" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" ht="36.75" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+    </row>
+    <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A4" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+    </row>
+    <row r="5" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="62"/>
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="D6" s="72"/>
+      <c r="E6" s="73"/>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="D7" s="74"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="21">
-        <v>22.0</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="62"/>
+      <c r="C8" s="5">
+        <v>22</v>
+      </c>
+      <c r="D8" s="72"/>
+      <c r="E8" s="73"/>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="21">
-        <v>2018.0</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" ht="21.0" customHeight="1">
-      <c r="A10" s="22"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" ht="27.75" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="5">
+        <v>2018</v>
+      </c>
+      <c r="D9" s="72"/>
+      <c r="E9" s="73"/>
+    </row>
+    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="75"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+    </row>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="24" t="s">
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+    </row>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26" t="s">
+      <c r="B12" s="78"/>
+      <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13" ht="27.75" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="78"/>
+      <c r="C13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" ht="27.75" customHeight="1">
-      <c r="A14" s="29" t="s">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="78"/>
+      <c r="C14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" ht="27.75" customHeight="1">
-      <c r="A15" s="29" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="78"/>
+      <c r="C15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" ht="27.75" customHeight="1">
-      <c r="A16" s="29" t="s">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="78"/>
+      <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="30"/>
-    </row>
-    <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="28" t="s">
+      <c r="B17" s="78"/>
+      <c r="C17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="30"/>
-    </row>
-    <row r="18" ht="27.75" customHeight="1">
-      <c r="A18" s="29" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="78"/>
+      <c r="C18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="30"/>
-    </row>
-    <row r="19" ht="27.75" customHeight="1">
-      <c r="A19" s="29" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="28" t="s">
+      <c r="B19" s="78"/>
+      <c r="C19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-    </row>
-    <row r="20" ht="27.75" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="78"/>
+      <c r="C20" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-    </row>
-    <row r="21" ht="27.75" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="28" t="s">
+      <c r="B21" s="78"/>
+      <c r="C21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-    </row>
-    <row r="22" ht="27.75" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="28" t="s">
+      <c r="B22" s="78"/>
+      <c r="C22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-    </row>
-    <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="29" t="s">
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="28" t="s">
+      <c r="B23" s="78"/>
+      <c r="C23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-    </row>
-    <row r="24" ht="27.75" customHeight="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-    </row>
-    <row r="25" ht="27.75" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-    </row>
-    <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="24" t="s">
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+    </row>
+    <row r="26" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="32" t="s">
+      <c r="B26" s="78"/>
+      <c r="C26" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-    </row>
-    <row r="27" ht="27.75" customHeight="1">
-      <c r="A27" s="29" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="33" t="s">
+      <c r="B27" s="78"/>
+      <c r="C27" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-    </row>
-    <row r="28" ht="27.75" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="33" t="s">
+      <c r="B28" s="78"/>
+      <c r="C28" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-    </row>
-    <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="29" t="s">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="33" t="s">
+      <c r="B29" s="78"/>
+      <c r="C29" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-    </row>
-    <row r="30" ht="27.75" customHeight="1">
-      <c r="A30" s="29" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="34" t="s">
+      <c r="B30" s="78"/>
+      <c r="C30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-    </row>
-    <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="30"/>
-    </row>
-    <row r="32" ht="27.75" customHeight="1">
-      <c r="A32" s="36" t="s">
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-    </row>
-    <row r="33" ht="27.75" customHeight="1">
-      <c r="A33" s="24" t="s">
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+    </row>
+    <row r="33" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="34" t="s">
+      <c r="B33" s="78"/>
+      <c r="C33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-    </row>
-    <row r="34" ht="27.75" customHeight="1">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-    </row>
-    <row r="35" ht="27.75" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-    </row>
-    <row r="36" ht="155.25" customHeight="1">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38" t="str">
-        <f>UNICHAR(10227)</f>
-        <v>⟳</v>
-      </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40" t="str">
-        <f>UNICHAR(10227)</f>
-        <v>⟳</v>
-      </c>
-      <c r="E36" s="37"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+    </row>
+    <row r="36" spans="1:5" ht="155.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15" t="e">
+        <f ca="1">_xludf.UNICHAR(10227)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17" t="e">
+        <f ca="1">_xludf.UNICHAR(10227)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E36" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
@@ -1752,559 +1886,533 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C33">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C33" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"County,Census Tract"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C27:C30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C27:C30" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Destroyed,Major,Minor"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C14:C23">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C14:C23" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"N,Y"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C13">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C13" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink display="Storm ID" location="'Data Dictionary'!B2" ref="A6"/>
-    <hyperlink display="Storm Name" location="'Data Dictionary'!B3" ref="A7"/>
-    <hyperlink display="Latest Advisory #" location="'Data Dictionary'!B4" ref="A8"/>
-    <hyperlink display="Storm Year" location="'Data Dictionary'!B5" ref="A9"/>
-    <hyperlink display="Occupancy Type" location="'Data Dictionary'!b6" ref="A12"/>
-    <hyperlink display="Single Family Dwelling" location="'Data Dictionary'!b7" ref="A13"/>
-    <hyperlink display="Manufactured/Mobile Home" location="'Data Dictionary'!b8" ref="A14"/>
-    <hyperlink display="Multi-Family Dwelling: Duplex" location="'Data Dictionary'!b9" ref="A15"/>
-    <hyperlink display="Multi-Family Dwelling: 3-4 units" location="'Data Dictionary'!b10" ref="A16"/>
-    <hyperlink display="Multi-Family Dwelling: 5-9 units" location="'Data Dictionary'!b11" ref="A17"/>
-    <hyperlink display="Multi-Family Dwelling: 10-19 units" location="'Data Dictionary'!b12" ref="A18"/>
-    <hyperlink display="Multi-Family Dwelling: 20-49 units" location="'Data Dictionary'!b13" ref="A19"/>
-    <hyperlink display="Multi-Family Dwelling: 50+ units" location="'Data Dictionary'!b14" ref="A20"/>
-    <hyperlink display="Temporary Lodging (Hotel/Motel)" location="'Data Dictionary'!b15" ref="A21"/>
-    <hyperlink display="Institutional Dormitory (group housing - military, college)" location="'Data Dictionary'!b16" ref="A22"/>
-    <hyperlink display="Nursing Home" location="'Data Dictionary'!b17" ref="A23"/>
-    <hyperlink display="Predicted Storm Surge Height" location="'Data Dictionary'!b18" ref="A26"/>
-    <hyperlink display="Category Label" location="'Data Dictionary'!b23" ref="C26"/>
-    <hyperlink display="&gt;9 feet" location="'Data Dictionary'!b19" ref="A27"/>
-    <hyperlink display="&gt;6 feet" location="'Data Dictionary'!b20" ref="A28"/>
-    <hyperlink display="&gt;3 feet" location="'Data Dictionary'!b21" ref="A29"/>
-    <hyperlink display="&gt;1 foot" location="'Data Dictionary'!b22" ref="A30"/>
-    <hyperlink display="Geography" location="'Data Dictionary'!b27" ref="A33"/>
+    <hyperlink ref="A6" location="'Data Dictionary'!B2" display="Storm ID" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A7" location="'Data Dictionary'!B3" display="Storm Name" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A8" location="'Data Dictionary'!B4" display="Latest Advisory #" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A9" location="'Data Dictionary'!B5" display="Storm Year" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A12" location="'Data Dictionary'!b6" display="Occupancy Type" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A13" location="'Data Dictionary'!b7" display="Single Family Dwelling" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A14" location="'Data Dictionary'!b8" display="Manufactured/Mobile Home" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A15" location="'Data Dictionary'!b9" display="Multi-Family Dwelling: Duplex" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A16" location="'Data Dictionary'!b10" display="Multi-Family Dwelling: 3-4 units" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A17" location="'Data Dictionary'!b11" display="Multi-Family Dwelling: 5-9 units" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A18" location="'Data Dictionary'!b12" display="Multi-Family Dwelling: 10-19 units" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A19" location="'Data Dictionary'!b13" display="Multi-Family Dwelling: 20-49 units" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A20" location="'Data Dictionary'!b14" display="Multi-Family Dwelling: 50+ units" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A21" location="'Data Dictionary'!b15" display="Temporary Lodging (Hotel/Motel)" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A22" location="'Data Dictionary'!b16" display="Institutional Dormitory (group housing - military, college)" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A23" location="'Data Dictionary'!b17" display="Nursing Home" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A26" location="'Data Dictionary'!b18" display="Predicted Storm Surge Height" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C26" location="'Data Dictionary'!b23" display="Category Label" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A27" location="'Data Dictionary'!b19" display="&gt;9 feet" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A28" location="'Data Dictionary'!b20" display="&gt;6 feet" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A29" location="'Data Dictionary'!b21" display="&gt;3 feet" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A30" location="'Data Dictionary'!b22" display="&gt;1 foot" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A33" location="'Data Dictionary'!b27" display="Geography" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
   </hyperlinks>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.67"/>
-    <col customWidth="1" min="2" max="2" width="47.44"/>
-    <col customWidth="1" min="3" max="3" width="72.0"/>
-    <col customWidth="1" min="4" max="5" width="24.67"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="47.4140625" customWidth="1"/>
+    <col min="3" max="3" width="72" customWidth="1"/>
+    <col min="4" max="5" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="22" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" ht="48.75" customHeight="1">
-      <c r="A2" s="46">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="47" t="s">
+    <row r="2" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="27" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="48.75" customHeight="1">
-      <c r="A3" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="52" t="s">
+    <row r="3" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="28">
+        <v>1</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" ht="48.75" customHeight="1">
-      <c r="A4" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="57" t="s">
+    <row r="4" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="32">
+        <v>1</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="36" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" ht="48.75" customHeight="1">
-      <c r="A5" s="61">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="62" t="s">
+    <row r="5" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="37">
+        <v>1</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" ht="62.25" customHeight="1">
-      <c r="A6" s="66">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="67" t="s">
+    <row r="6" spans="1:5" ht="62.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="41">
+        <v>2</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="70"/>
-    </row>
-    <row r="7" ht="51.0" customHeight="1">
-      <c r="A7" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B7" s="72" t="s">
+      <c r="D6" s="44"/>
+      <c r="E6" s="45"/>
+    </row>
+    <row r="7" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="32">
+        <v>2</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" ht="51.0" customHeight="1">
-      <c r="A8" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="72" t="s">
+    <row r="8" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="32">
+        <v>2</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" ht="51.0" customHeight="1">
-      <c r="A9" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="72" t="s">
+    <row r="9" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="32">
+        <v>2</v>
+      </c>
+      <c r="B9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B10" s="72" t="s">
+    <row r="10" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="32">
+        <v>2</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" ht="51.0" customHeight="1">
-      <c r="A11" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B11" s="72" t="s">
+    <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="32">
+        <v>2</v>
+      </c>
+      <c r="B11" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" ht="51.0" customHeight="1">
-      <c r="A12" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B12" s="72" t="s">
+    <row r="12" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32">
+        <v>2</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="73" t="s">
+      <c r="E12" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" ht="51.0" customHeight="1">
-      <c r="A13" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B13" s="72" t="s">
+    <row r="13" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="32">
+        <v>2</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" ht="51.0" customHeight="1">
-      <c r="A14" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B14" s="72" t="s">
+    <row r="14" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32">
+        <v>2</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="74" t="s">
+      <c r="C14" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" ht="51.0" customHeight="1">
-      <c r="A15" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B15" s="72" t="s">
+    <row r="15" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32">
+        <v>2</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="E15" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" ht="51.0" customHeight="1">
-      <c r="A16" s="71">
-        <v>2.0</v>
-      </c>
-      <c r="B16" s="72" t="s">
+    <row r="16" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="32">
+        <v>2</v>
+      </c>
+      <c r="B16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="73" t="s">
+      <c r="E16" s="46" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" ht="51.0" customHeight="1">
-      <c r="A17" s="75">
-        <v>2.0</v>
-      </c>
-      <c r="B17" s="76" t="s">
+    <row r="17" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="48">
+        <v>2</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="51" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" ht="51.0" customHeight="1">
-      <c r="A18" s="66">
-        <v>3.0</v>
-      </c>
-      <c r="B18" s="67" t="s">
+    <row r="18" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="41">
+        <v>3</v>
+      </c>
+      <c r="B18" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="80"/>
-    </row>
-    <row r="19" ht="51.0" customHeight="1">
-      <c r="A19" s="71">
-        <v>3.0</v>
-      </c>
-      <c r="B19" s="72" t="s">
+      <c r="D18" s="52"/>
+      <c r="E18" s="53"/>
+    </row>
+    <row r="19" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32">
+        <v>3</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="46" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" ht="51.0" customHeight="1">
-      <c r="A20" s="71">
-        <v>3.0</v>
-      </c>
-      <c r="B20" s="72" t="s">
+    <row r="20" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="32">
+        <v>3</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="73" t="s">
+      <c r="E20" s="46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" ht="51.0" customHeight="1">
-      <c r="A21" s="71">
-        <v>3.0</v>
-      </c>
-      <c r="B21" s="72" t="s">
+    <row r="21" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="32">
+        <v>3</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="46" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" ht="51.0" customHeight="1">
-      <c r="A22" s="75">
-        <v>3.0</v>
-      </c>
-      <c r="B22" s="76" t="s">
+    <row r="22" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="48">
+        <v>3</v>
+      </c>
+      <c r="B22" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="81" t="s">
+      <c r="D22" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="51" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" ht="51.0" customHeight="1">
-      <c r="A23" s="82">
-        <v>3.0</v>
-      </c>
-      <c r="B23" s="83" t="s">
+    <row r="23" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="55">
+        <v>3</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="86"/>
-    </row>
-    <row r="24" ht="51.0" customHeight="1">
-      <c r="A24" s="71">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="72" t="s">
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
+    </row>
+    <row r="24" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="32">
+        <v>3</v>
+      </c>
+      <c r="B24" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="87"/>
-    </row>
-    <row r="25" ht="51.0" customHeight="1">
-      <c r="A25" s="71">
-        <v>3.0</v>
-      </c>
-      <c r="B25" s="72" t="s">
+      <c r="D24" s="33"/>
+      <c r="E24" s="46"/>
+    </row>
+    <row r="25" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="32">
+        <v>3</v>
+      </c>
+      <c r="B25" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="87"/>
-    </row>
-    <row r="26" ht="51.0" customHeight="1">
-      <c r="A26" s="75">
-        <v>3.0</v>
-      </c>
-      <c r="B26" s="76" t="s">
+      <c r="D25" s="33"/>
+      <c r="E25" s="46"/>
+    </row>
+    <row r="26" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="48">
+        <v>3</v>
+      </c>
+      <c r="B26" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="88"/>
-      <c r="E26" s="89"/>
-    </row>
-    <row r="27" ht="51.0" customHeight="1">
-      <c r="A27" s="66">
-        <v>4.0</v>
-      </c>
-      <c r="B27" s="67" t="s">
+      <c r="D26" s="49"/>
+      <c r="E26" s="51"/>
+    </row>
+    <row r="27" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="41">
+        <v>4</v>
+      </c>
+      <c r="B27" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="90" t="s">
+      <c r="E27" s="59" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" ht="51.0" customHeight="1">
-      <c r="A28" s="71">
-        <v>4.0</v>
-      </c>
-      <c r="B28" s="72" t="s">
+    <row r="28" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32">
+        <v>4</v>
+      </c>
+      <c r="B28" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="74" t="s">
+      <c r="C28" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="91"/>
-      <c r="E28" s="73"/>
-    </row>
-    <row r="29" ht="51.0" customHeight="1">
-      <c r="A29" s="75">
-        <v>4.0</v>
-      </c>
-      <c r="B29" s="76" t="s">
+      <c r="D28" s="60"/>
+      <c r="E28" s="46"/>
+    </row>
+    <row r="29" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48">
+        <v>4</v>
+      </c>
+      <c r="B29" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="76"/>
-      <c r="E29" s="89"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="51"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/ARC Storm Surge Shelter Demand.xlsx
+++ b/data/ARC Storm Surge Shelter Demand.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/54fa78dadb255002/Documents/Heinz/Spring 2026/94-739 Capstone/ARC_Capstone/notebooks/repo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/54fa78dadb255002/Documents/Heinz/Spring 2026/94-739 Capstone/ARC_Capstone/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9AB5DFE02E429FF0E24E20D6E25A8F1C4D155B9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_9AB5DFE02E429FF0E24E20D6E25A8F1C4D155B9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9942B9D2-F76F-441C-A1C5-042FFA90DE54}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2240" windowWidth="16800" windowHeight="9670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interface" sheetId="1" r:id="rId1"/>
@@ -111,13 +111,7 @@
     <t>Storm ID</t>
   </si>
   <si>
-    <t>AL142018</t>
-  </si>
-  <si>
     <t>Storm Name</t>
-  </si>
-  <si>
-    <t>Michael</t>
   </si>
   <si>
     <t>Latest Advisory #</t>
@@ -437,6 +431,12 @@
   </si>
   <si>
     <t>Census tract-level aggregation</t>
+  </si>
+  <si>
+    <t>AL092024</t>
+  </si>
+  <si>
+    <t>Helene</t>
   </si>
 </sst>
 </file>
@@ -1131,6 +1131,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1157,27 +1177,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1487,40 +1487,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
     </row>
     <row r="2" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="76"/>
     </row>
     <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
     </row>
     <row r="5" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -1530,194 +1530,194 @@
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="62"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="80"/>
+      <c r="E6" s="62"/>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="73"/>
-    </row>
-    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="61" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="5" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="5">
+        <v>16</v>
+      </c>
+      <c r="D8" s="80"/>
+      <c r="E8" s="62"/>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="63" t="s">
+      <c r="B9" s="70"/>
+      <c r="C9" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="80"/>
+      <c r="E9" s="62"/>
+    </row>
+    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="67"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+    </row>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="5">
-        <v>22</v>
-      </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="73"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="63" t="s">
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+    </row>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="5">
-        <v>2018</v>
-      </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="73"/>
-    </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="75"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-    </row>
-    <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="76" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-    </row>
-    <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="78"/>
+      <c r="A13" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="64"/>
       <c r="C13" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="78"/>
+      <c r="A14" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="64"/>
       <c r="C14" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="80" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="78"/>
+      <c r="A15" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="64"/>
       <c r="C15" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="78"/>
+      <c r="A16" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="64"/>
       <c r="C16" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="78"/>
+      <c r="A17" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="64"/>
       <c r="C17" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="78"/>
+      <c r="A18" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="64"/>
       <c r="C18" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="78"/>
+      <c r="A19" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="64"/>
       <c r="C19" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="80" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="78"/>
+      <c r="A20" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="64"/>
       <c r="C20" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
     </row>
     <row r="21" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="78"/>
+      <c r="A21" s="63" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="64"/>
       <c r="C21" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="78"/>
+      <c r="A22" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="64"/>
       <c r="C22" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="80" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="78"/>
+      <c r="A23" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="64"/>
       <c r="C23" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -1730,65 +1730,65 @@
       <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+    </row>
+    <row r="26" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="64"/>
+      <c r="C26" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-    </row>
-    <row r="26" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="78"/>
+      <c r="A27" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="64"/>
       <c r="C27" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="80" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="78"/>
+      <c r="A28" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="64"/>
       <c r="C28" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="78"/>
+      <c r="A29" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="64"/>
       <c r="C29" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="78"/>
+      <c r="A30" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="64"/>
       <c r="C30" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -1801,21 +1801,21 @@
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+    </row>
+    <row r="33" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="64"/>
+      <c r="C33" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-    </row>
-    <row r="33" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="12" t="s">
-        <v>38</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1828,13 +1828,13 @@
       <c r="E34" s="9"/>
     </row>
     <row r="35" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
+      <c r="A35" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
     </row>
     <row r="36" spans="1:5" ht="155.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="14"/>
@@ -1851,29 +1851,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
@@ -1886,6 +1863,29 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C33" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1949,19 +1949,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="D1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="E1" s="22" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1972,13 +1972,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>45</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1986,16 +1986,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -2003,16 +2003,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -2020,16 +2020,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="40" t="s">
         <v>52</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="62.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2037,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="45"/>
@@ -2050,16 +2050,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="46" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2067,16 +2067,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2084,16 +2084,16 @@
         <v>2</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2101,16 +2101,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2118,16 +2118,16 @@
         <v>2</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2135,16 +2135,16 @@
         <v>2</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2152,16 +2152,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2169,16 +2169,16 @@
         <v>2</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2186,16 +2186,16 @@
         <v>2</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2203,16 +2203,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2220,16 +2220,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2237,10 +2237,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" s="52"/>
       <c r="E18" s="53"/>
@@ -2250,16 +2250,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="46" t="s">
         <v>69</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2267,16 +2267,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2284,16 +2284,16 @@
         <v>3</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2301,16 +2301,16 @@
         <v>3</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2318,10 +2318,10 @@
         <v>3</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="59"/>
@@ -2331,10 +2331,10 @@
         <v>3</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="46"/>
@@ -2344,10 +2344,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D25" s="33"/>
       <c r="E25" s="46"/>
@@ -2357,10 +2357,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="51"/>
@@ -2370,16 +2370,16 @@
         <v>4</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
@@ -2387,10 +2387,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28" s="60"/>
       <c r="E28" s="46"/>
@@ -2400,10 +2400,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="51"/>
